--- a/DailyTracker.xlsx
+++ b/DailyTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nagarjuna\OneDrive\Desktop\Automation\PlaywrightAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1FD758-56A4-47F9-BB83-4B57F06C5196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACB3D99-8665-45EC-AE54-2E3BB986EA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <r>
       <t>Spread operator (</t>
@@ -54,9 +54,6 @@
     <t>Destructuring</t>
   </si>
   <si>
-    <t>12. Primitive types:</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
   </si>
   <si>
     <t>boolean</t>
-  </si>
-  <si>
-    <t>13. Special types:</t>
   </si>
   <si>
     <t>any</t>
@@ -471,6 +465,12 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>Primitive types:</t>
+  </si>
+  <si>
+    <t>Special types:</t>
   </si>
 </sst>
 </file>
@@ -813,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C127"/>
+  <dimension ref="A2:C126"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41.453125" customWidth="1"/>
@@ -824,10 +824,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -835,10 +835,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -846,7 +846,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -854,10 +857,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -865,10 +868,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -876,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -884,7 +887,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -892,7 +895,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -910,360 +913,360 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="B13" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="23.5">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="26" spans="2:2" ht="23.5">
+    <row r="15" spans="1:3">
+      <c r="B15" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="23.5">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="1:2">
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="4" t="s">
-        <v>5</v>
-      </c>
+    <row r="32" spans="1:2">
+      <c r="B32" s="2"/>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="2"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="4" t="s">
+      <c r="B34" s="2"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="2"/>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="23.5">
+      <c r="B46" s="1"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" ht="23.5">
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="2"/>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" ht="23.5">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" ht="23.5">
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" ht="23.5">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="2"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="23.5">
-      <c r="B65" s="1"/>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="2"/>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" ht="23.5">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" ht="23.5">
-      <c r="B74" s="1"/>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="2"/>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" ht="23.5">
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="2"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" ht="23.5">
-      <c r="B85" s="1"/>
-    </row>
-    <row r="86" spans="2:2">
-      <c r="B86" s="2"/>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="2" t="s">
+    <row r="94" spans="2:2" ht="23.5">
+      <c r="B94" s="1"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="2"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="23.5">
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="2"/>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" ht="23.5">
+      <c r="B103" s="1"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="2"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" ht="23.5">
-      <c r="B104" s="1"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="2"/>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" ht="23.5">
+      <c r="B111" s="1"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="2"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="2:2">
-      <c r="B108" s="2" t="s">
+    <row r="114" spans="2:2">
+      <c r="B114" s="2"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="112" spans="2:2" ht="23.5">
-      <c r="B112" s="1"/>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="2"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="2"/>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="2"/>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="2"/>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/DailyTracker.xlsx
+++ b/DailyTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nagarjuna\OneDrive\Desktop\Automation\PlaywrightAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACB3D99-8665-45EC-AE54-2E3BB986EA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A57403-C88B-44BA-A5D7-7D4479E34289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
   <si>
     <r>
       <t>Spread operator (</t>
@@ -471,6 +471,33 @@
   </si>
   <si>
     <t>Special types:</t>
+  </si>
+  <si>
+    <t>Control Statements</t>
+  </si>
+  <si>
+    <t>if else</t>
+  </si>
+  <si>
+    <t>switch</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>while</t>
+  </si>
+  <si>
+    <t>for of</t>
+  </si>
+  <si>
+    <t>for in</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>continue</t>
   </si>
 </sst>
 </file>
@@ -813,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C126"/>
+  <dimension ref="A2:C125"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41.453125" customWidth="1"/>
@@ -881,6 +908,9 @@
       <c r="B7" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
@@ -933,18 +963,27 @@
       <c r="B15" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="B16" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="B17" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>13</v>
       </c>
@@ -952,320 +991,374 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:3">
       <c r="B19" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="B20" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="B22" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="23.5">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="32" spans="1:2">
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="B26" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="B29" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="B30" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="2"/>
+    <row r="38" spans="2:2">
+      <c r="B38" s="2"/>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:2" ht="23.5">
-      <c r="B46" s="1"/>
+    <row r="45" spans="2:2" ht="23.5">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="2"/>
     </row>
     <row r="47" spans="2:2">
-      <c r="B47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="23.5">
-      <c r="B56" s="1"/>
+    <row r="55" spans="2:2" ht="23.5">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="2"/>
     </row>
     <row r="57" spans="2:2">
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="2:2" ht="23.5">
-      <c r="B64" s="1"/>
+    <row r="63" spans="2:2" ht="23.5">
+      <c r="B63" s="1"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="2"/>
     </row>
     <row r="65" spans="2:2">
-      <c r="B65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="2:2" ht="23.5">
-      <c r="B73" s="1"/>
+    <row r="72" spans="2:2" ht="23.5">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="2"/>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="23.5">
-      <c r="B84" s="1"/>
+    <row r="83" spans="2:2" ht="23.5">
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="2"/>
     </row>
     <row r="85" spans="2:2">
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="2:2">
-      <c r="B89" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="4" t="s">
+      <c r="B89" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="94" spans="2:2" ht="23.5">
-      <c r="B94" s="1"/>
+    <row r="93" spans="2:2" ht="23.5">
+      <c r="B93" s="1"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="2"/>
     </row>
     <row r="95" spans="2:2">
-      <c r="B95" s="2"/>
+      <c r="B95" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="2:2" ht="23.5">
-      <c r="B103" s="1"/>
+    <row r="102" spans="2:2" ht="23.5">
+      <c r="B102" s="1"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="2"/>
     </row>
     <row r="104" spans="2:2">
-      <c r="B104" s="2"/>
+      <c r="B104" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="111" spans="2:2" ht="23.5">
-      <c r="B111" s="1"/>
+    <row r="110" spans="2:2" ht="23.5">
+      <c r="B110" s="1"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="2"/>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="2"/>
+      <c r="B112" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="B113" s="2"/>
     </row>
     <row r="114" spans="2:2">
-      <c r="B114" s="2"/>
+      <c r="B114" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B118" s="2"/>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="2"/>
+      <c r="B119" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="2" t="s">
         <v>53</v>
       </c>
     </row>

--- a/DailyTracker.xlsx
+++ b/DailyTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nagarjuna\OneDrive\Desktop\Automation\PlaywrightAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A57403-C88B-44BA-A5D7-7D4479E34289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398C92B5-F78F-486E-8766-ED2B5650C419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
   <si>
     <r>
       <t>Spread operator (</t>
@@ -498,6 +498,9 @@
   </si>
   <si>
     <t>continue</t>
+  </si>
+  <si>
+    <t>advance iteration yet to cover</t>
   </si>
 </sst>
 </file>
@@ -840,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C125"/>
+  <dimension ref="A2:D125"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41.453125" customWidth="1"/>
@@ -975,7 +978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="B17" s="4" t="s">
         <v>4</v>
       </c>
@@ -983,7 +986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>13</v>
       </c>
@@ -991,7 +994,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:4">
       <c r="B19" s="4" t="s">
         <v>5</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:4">
       <c r="B20" s="4" t="s">
         <v>6</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:4">
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
@@ -1015,12 +1018,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:4">
       <c r="B22" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>14</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:4">
       <c r="B24" s="4" t="s">
         <v>68</v>
       </c>
@@ -1036,45 +1039,57 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:4">
       <c r="B25" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+    </row>
+    <row r="26" spans="1:4">
       <c r="B26" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="B27" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="B28" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="B29" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="B30" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:4">
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:4">
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="2:2">

--- a/DailyTracker.xlsx
+++ b/DailyTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nagarjuna\OneDrive\Desktop\Automation\PlaywrightAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398C92B5-F78F-486E-8766-ED2B5650C419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6330ED-CD91-42C8-8142-4FE03AC3CA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
   <si>
     <r>
       <t>Spread operator (</t>
@@ -75,15 +75,6 @@
     <t>never</t>
   </si>
   <si>
-    <t>14. Arrays</t>
-  </si>
-  <si>
-    <t>15. Tuples</t>
-  </si>
-  <si>
-    <t>16. Type inference</t>
-  </si>
-  <si>
     <t>17. Function types</t>
   </si>
   <si>
@@ -501,6 +492,18 @@
   </si>
   <si>
     <t>advance iteration yet to cover</t>
+  </si>
+  <si>
+    <t>Array</t>
+  </si>
+  <si>
+    <t>User Defined Data Types</t>
+  </si>
+  <si>
+    <t>Tuple</t>
+  </si>
+  <si>
+    <t>Enum</t>
   </si>
 </sst>
 </file>
@@ -854,10 +857,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -865,10 +868,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -876,10 +879,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -887,10 +890,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -898,10 +901,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -909,10 +912,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -920,7 +923,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -928,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -946,12 +949,12 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -959,7 +962,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -967,7 +970,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -975,7 +978,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -983,7 +986,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -991,7 +994,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -999,7 +1002,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1007,7 +1010,7 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1015,7 +1018,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1028,120 +1031,143 @@
         <v>14</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="B26" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="B28" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="B30" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="B31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>15</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="38" spans="2:2">
+    <row r="33" spans="2:3">
+      <c r="B33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:3">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41" s="2"/>
+    </row>
+    <row r="45" spans="2:3" ht="23.5">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="2" t="s">
+    <row r="48" spans="2:3">
+      <c r="B48" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" ht="23.5">
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="2"/>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="23.5">
@@ -1152,17 +1178,17 @@
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="2:2" ht="23.5">
@@ -1173,22 +1199,22 @@
     </row>
     <row r="65" spans="2:2">
       <c r="B65" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="2:2" ht="23.5">
@@ -1199,32 +1225,32 @@
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="2:2" ht="23.5">
@@ -1235,27 +1261,27 @@
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="23.5">
@@ -1266,22 +1292,22 @@
     </row>
     <row r="95" spans="2:2">
       <c r="B95" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="2:2" ht="23.5">
@@ -1292,17 +1318,17 @@
     </row>
     <row r="104" spans="2:2">
       <c r="B104" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="2:2" ht="23.5">
@@ -1313,7 +1339,7 @@
     </row>
     <row r="112" spans="2:2">
       <c r="B112" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113" spans="2:2">
@@ -1321,22 +1347,22 @@
     </row>
     <row r="114" spans="2:2">
       <c r="B114" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118" spans="2:2">
@@ -1344,37 +1370,37 @@
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/DailyTracker.xlsx
+++ b/DailyTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nagarjuna\OneDrive\Desktop\Automation\PlaywrightAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6330ED-CD91-42C8-8142-4FE03AC3CA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0536F8C-E97E-4BE1-B859-D0FCC1DB0135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
   <si>
     <r>
       <t>Spread operator (</t>
@@ -504,6 +504,24 @@
   </si>
   <si>
     <t>Enum</t>
+  </si>
+  <si>
+    <t>Introduction To Playwright</t>
+  </si>
+  <si>
+    <t>VS Code Installation</t>
+  </si>
+  <si>
+    <t>node js</t>
+  </si>
+  <si>
+    <t>Playwright Installation</t>
+  </si>
+  <si>
+    <t>Implement Test</t>
+  </si>
+  <si>
+    <t>import playwright annotation</t>
   </si>
 </sst>
 </file>
@@ -1121,6 +1139,9 @@
       <c r="B34" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="35" spans="2:3">
       <c r="B35" s="2" t="s">
@@ -1410,9 +1431,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E76B105-C6C7-47B2-B9FE-447F67FB5676}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:C7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="C4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DailyTracker.xlsx
+++ b/DailyTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nagarjuna\OneDrive\Desktop\Automation\PlaywrightAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0536F8C-E97E-4BE1-B859-D0FCC1DB0135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FCBFAC-32A8-4E55-9C62-B88375B012BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="85">
   <si>
     <r>
       <t>Spread operator (</t>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>import playwright annotation</t>
+  </si>
+  <si>
+    <t>literals</t>
   </si>
 </sst>
 </file>
@@ -1147,6 +1150,17 @@
       <c r="B35" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="38" spans="2:3">
       <c r="B38" s="2"/>
